--- a/maintenance_forms/005_equipment_maintenance_request_form--maintenance_forms.xlsx
+++ b/maintenance_forms/005_equipment_maintenance_request_form--maintenance_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -838,8 +838,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -867,12 +867,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'equipment_1'}</t>
+          <t>equipment_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Equipment 1'}</t>
+          <t>Equipment 1</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'equipment_2'}</t>
+          <t>equipment_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Equipment 2'}</t>
+          <t>Equipment 2</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'available'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Available'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'under_maintenance'}</t>
+          <t>under_maintenance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Under Maintenance'}</t>
+          <t>Under Maintenance</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Offline'}</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'staff'}</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Staff'}</t>
+          <t>Staff</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'contractor'}</t>
+          <t>contractor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Contractor'}</t>
+          <t>Contractor</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'external'}</t>
+          <t>external</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'External'}</t>
+          <t>External</t>
         </is>
       </c>
     </row>
